--- a/Analysis/Output/data_dictionary_merged_clean.xlsx
+++ b/Analysis/Output/data_dictionary_merged_clean.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -420,17 +420,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>date_of_interview</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Date of Interview</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E3">
@@ -443,21 +443,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Year of study</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fct</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E4">
-        <v>2805</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -466,12 +466,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>agegrps</t>
+          <t>study</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Age group</t>
+          <t>Year of study</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="6">
@@ -489,12 +489,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>agegrps</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Age group</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -512,12 +512,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>marstat</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marital Status</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -535,12 +535,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>h_head</t>
+          <t>marstat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Household head</t>
+          <t>Marital Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -558,12 +558,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>activitylevel</t>
+          <t>h_head</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Activity Level</t>
+          <t>Household head</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -581,12 +581,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>activitylevel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Social media use</t>
+          <t>Activity Level</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>supportive</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Supportive</t>
+          <t>Social media use</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>2805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -627,12 +627,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>incomesource</t>
+          <t>supportive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Source of Income</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>incomesource</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Source of Income</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mh_services</t>
+          <t>awareness</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mental Health Sevices</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gad7_1</t>
+          <t>mh_services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1. Feeling nervous, anxious, or on edge</t>
+          <t>Mental Health Sevices</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="16">
@@ -719,12 +719,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gad7_2</t>
+          <t>gad7_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2. Not being able to stop or control worrying</t>
+          <t>1. Feeling nervous, anxious, or on edge</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gad7_3</t>
+          <t>gad7_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3. Worrying too much about different things</t>
+          <t>2. Not being able to stop or control worrying</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gad7_4</t>
+          <t>gad7_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4. Trouble relaxing</t>
+          <t>3. Worrying too much about different things</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gad7_5</t>
+          <t>gad7_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5. Being so restless that it's hard to sit still</t>
+          <t>4. Trouble relaxing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gad7_6</t>
+          <t>gad7_5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6. Becoming easily annoyed or Irritable</t>
+          <t>5. Being so restless that it's hard to sit still</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gad7_7</t>
+          <t>gad7_6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7. Feeling afraid as if something awful might happen</t>
+          <t>6. Becoming easily annoyed or Irritable</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gad7_total_score</t>
+          <t>gad7_7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GAD-7 Total Score</t>
+          <t>7. Feeling afraid as if something awful might happen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>fct</t>
         </is>
       </c>
       <c r="E22">
@@ -880,17 +880,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gad7_anxiety</t>
+          <t>gad7_total_score</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GAD-7 Anxiety</t>
+          <t>GAD-7 Total Score</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>fct</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E23">
@@ -903,12 +903,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>phq9_1</t>
+          <t>gad7_anxiety</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1. Little interest or pleasure in doing things</t>
+          <t>GAD-7 Anxiety</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>phq9_2</t>
+          <t>phq9_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2. Feeling down, depressed, or hopeless</t>
+          <t>1. Little interest or pleasure in doing things</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>phq9_3</t>
+          <t>phq9_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3. Trouble falling or staying asleep, or sleeping too much</t>
+          <t>2. Feeling down, depressed, or hopeless</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>phq9_4</t>
+          <t>phq9_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4. Feeling tired or having little energy</t>
+          <t>3. Trouble falling or staying asleep, or sleeping too much</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>phq9_5</t>
+          <t>phq9_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5. Poor appetite or overeating</t>
+          <t>4. Feeling tired or having little energy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>phq9_6</t>
+          <t>phq9_5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6. Feeling bad about yourself or that you are a failure or have let yourself or your family down</t>
+          <t>5. Poor appetite or overeating</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>phq9_7</t>
+          <t>phq9_6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7. Trouble concentrating on things</t>
+          <t>6. Feeling bad about yourself or that you are a failure or have let yourself or your family down</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>phq9_8</t>
+          <t>phq9_7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8. Moving or speaking so slowly or being so fidgety or restless that you have been moving around a lot more than usual</t>
+          <t>7. Trouble concentrating on things</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>phq9_9</t>
+          <t>phq9_8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9. Thoughts that you would be better off dead or of hurting yourself in some way</t>
+          <t>8. Moving or speaking so slowly or being so fidgety or restless that you have been moving around a lot more than usual</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1110,17 +1110,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>phq9_totalscore</t>
+          <t>phq9_9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PHQ-9 Total Score</t>
+          <t>9. Thoughts that you would be better off dead or of hurting yourself in some way</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>fct</t>
         </is>
       </c>
       <c r="E33">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>phq9_depression</t>
+          <t>phq9_totalscore</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PHQ-9 Depression</t>
+          <t>PHQ-9 Total Score</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>fct</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E34">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>psq_hypomania</t>
+          <t>phq9_depression</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Have there been times when you felt very happy indeed without a break for days on end?</t>
+          <t>PHQ-9 Depression</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>psq_hypomania2</t>
+          <t>psq_hypomania</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Was there an obvious reason for this and did your relatives or friends think it was strange or complain about it?</t>
+          <t>Have there been times when you felt very happy indeed without a break for days on end?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>psq_thoughtinsertion</t>
+          <t>psq_hypomania2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Have you ever felt that your thoughts were directly interfered with or controlled by some outside force or person?</t>
+          <t>Was there an obvious reason for this and did your relatives or friends think it was strange or complain about it?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>psq_thoughtinsertion2</t>
+          <t>psq_thoughtinsertion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Did this come about in a way that many people would find hard to believe, for instance, through telepathy?</t>
+          <t>Have you ever felt that your thoughts were directly interfered with or controlled by some outside force or person?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>psq_paranoia</t>
+          <t>psq_thoughtinsertion2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Have there been times when you felt that people were against you?</t>
+          <t>Did this come about in a way that many people would find hard to believe, for instance, through telepathy?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>psq_paranoia2</t>
+          <t>psq_paranoia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Have there been times when you felt that people were deliberately acting to harm you or your interests?</t>
+          <t>Have there been times when you felt that people were against you?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>psq_strangeexperiences</t>
+          <t>psq_paranoia2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Have there been times when you felt that something strange was going on?</t>
+          <t>Have there been times when you felt that people were deliberately acting to harm you or your interests?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>psq_strangeexperiences2</t>
+          <t>psq_strangeexperiences</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Did you feel it was so strange that other people would find it very hard to believe?</t>
+          <t>Have there been times when you felt that something strange was going on?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>psq_hallucinations</t>
+          <t>psq_strangeexperiences2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Have there been times when you heard or saw things that other people couldn’t?</t>
+          <t>Did you feel it was so strange that other people would find it very hard to believe?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>psq_hallucinations2</t>
+          <t>psq_hallucinations</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Did you at any time hear voices saying quite a few words or sentences when there was no one around that might account for it?</t>
+          <t>Have there been times when you heard or saw things that other people couldn’t?</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>psq_psychosis</t>
+          <t>psq_hallucinations2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PSQ Psychosis</t>
+          <t>Did you at any time hear voices saying quite a few words or sentences when there was no one around that might account for it?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>psq_totalscore</t>
+          <t>psq_psychosis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PSQ Total score</t>
+          <t>PSQ Psychosis</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>fct</t>
         </is>
       </c>
       <c r="E46">
@@ -1432,21 +1432,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>psq_totalscore</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Level of Education</t>
+          <t>PSQ Total score</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>fct</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1455,20 +1455,89 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Level of Education</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>site</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Study Population</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>fct</t>
-        </is>
-      </c>
-      <c r="E48">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>gad7_anxiety_severity</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>GAD-7 Anxiety Severity</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>phq9_depression_severity</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PHQ-9 Depression Severity</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E51">
         <v>0</v>
       </c>
     </row>
